--- a/test-output/TestResults.xlsx
+++ b/test-output/TestResults.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -26,6 +26,18 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Hotel Adult Count</t>
+  </si>
+  <si>
+    <t>Should reach maximum adults</t>
+  </si>
+  <si>
+    <t>Max adults: 12</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>Gift Card Validation</t>
   </si>
   <si>
@@ -33,18 +45,6 @@
   </si>
   <si>
     <t>Error: Email adress is Required and it should be valid</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Hotel Adult Count</t>
-  </si>
-  <si>
-    <t>Should reach maximum adults</t>
-  </si>
-  <si>
-    <t>Max adults: 12</t>
   </si>
   <si>
     <t>Cab Booking</t>
@@ -110,8 +110,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
@@ -124,7 +130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="18.5625"/>
@@ -189,6 +195,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="11">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
